--- a/hotelbeds_29-07_06-08_revisao.xlsx
+++ b/hotelbeds_29-07_06-08_revisao.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumo por fatura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Detalhe por noite" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +44,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,10 +59,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,16 +431,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,12 +453,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Data fatura</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Hóspede</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -463,15 +468,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Linhas</t>
+          <t>Nº linhas</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Total EUR</t>
+          <t>Total c/IVA (EUR)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ajuste arredond.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Correção de data</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -506,6 +521,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -539,6 +564,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>+0,01 na última linha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -572,6 +607,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -605,6 +650,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -638,6 +693,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -671,6 +736,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -704,6 +779,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -737,6 +822,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -770,6 +865,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -803,6 +908,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -836,6 +951,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>-0,01 na última linha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -869,6 +994,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -902,6 +1037,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -935,6 +1080,16 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -968,6 +1123,16 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -1001,6 +1166,16 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -1034,6 +1209,16 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -1067,6 +1252,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -1100,6 +1295,16 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -1133,6 +1338,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
@@ -1166,15 +1381,25 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>prepared</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -1185,7 +1410,1407 @@
       <c r="F23" s="2" t="n">
         <v>3914.72</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Nº Fatura</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Hóspede</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Booking Nº</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Data do serviço (noite)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Noites</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Qtd</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Preço c/IVA</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>IVA %</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Moeda</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>141253</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ISABELLA FRAGALA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>59-5913161</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>115.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>141253</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ISABELLA FRAGALA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>59-5913161</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>115.52</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>141253</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ISABELLA FRAGALA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>59-5913161</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>115.52</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>141253</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ISABELLA FRAGALA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>59-5913161</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>115.52</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>141252</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AERNIO DILKIN PENTEADO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>59-5813132</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>141252</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AERNIO DILKIN PENTEADO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>59-5813132</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>96.53</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>141251</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KYUWON KIM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>59-5972230</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>141250</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AERNIO DILKIN PENTEADO JUNIOR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>59-5813137</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>188</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>141250</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AERNIO DILKIN PENTEADO JUNIOR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>59-5813137</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>188</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>141249</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MARIA GRAZIA ACCORDINO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>59-5870877</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>192</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>141249</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MARIA GRAZIA ACCORDINO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>59-5870877</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>192</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>141188</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ERAN BARSHESHET</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>59-5975628</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>141132</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GENEVIEVE GEOFFROY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>59-5918399</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>141132</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GENEVIEVE GEOFFROY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>59-5918399</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>03-08-2026</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>141086</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EDOARDO SORVILLO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>59-5796065</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>141086</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EDOARDO SORVILLO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>59-5796065</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>141032</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL SANCHEZ MUNOZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>59-5966219</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>31-07-2026</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>141032</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL SANCHEZ MUNOZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>59-5966219</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>141031</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ADRIAN SANCHEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>59-5966219</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>31-07-2026</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>141031</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ADRIAN SANCHEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>59-5966219</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>141030</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ALBERTO SANTINI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>59-5924461</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>31-07-2026</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>97.29000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>141030</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ALBERTO SANTINI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>59-5924461</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>141029</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLAUDIA PESCE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>59-5924562</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>141028</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MARCO BASSAN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>59-5924562</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>204</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>141027</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FABIO JOSE COSTA CARDOSO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>59-5967246</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>141026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>THOMAS ELIZEO ZEKE SMITH</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>59-5944827</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>01-08-2026</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>140910</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MICHELLE SIMONE CHODOR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>59-5742516</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>29-07-2026</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>140910</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MICHELLE SIMONE CHODOR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>59-5742516</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>30-07-2026</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>140909</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SEBASTIANO ANTONIOLI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>59-5923902</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>30-07-2026</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>140874</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SIMONE MASARATI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>59-5744228</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>29-07-2026</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>172</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>140873</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DAVID JAMES FITZPATRICK</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>59-5865302</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>29-07-2026</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>140872</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FABIOLA BLANTE MARTINS ROSA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>59-5967338</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>29-07-2026</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>140810</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JOSE CARLOS SANCHEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>59-5951339</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>27-07-2026</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>140810</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JOSE CARLOS SANCHEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>59-5951339</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>28-07-2026</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
